--- a/assessment_forms/018_child_health_assessment_form--assessment_forms.xlsx
+++ b/assessment_forms/018_child_health_assessment_form--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -993,8 +993,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'male',_'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Male', 'value': 'male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'female',_'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Female', 'value': 'female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'asthma_or_respiratory',_'value':_'asthma'}</t>
+          <t>asthma_or_respiratory</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Asthma or Respiratory', 'value': 'asthma'}</t>
+          <t>Asthma or Respiratory</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'diabetes_or_endocrine',_'value':_'diabetes'}</t>
+          <t>diabetes_or_endocrine</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Diabetes or Endocrine', 'value': 'diabetes'}</t>
+          <t>Diabetes or Endocrine</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'seizures_or_neurological',_'value':_'seizures'}</t>
+          <t>seizures_or_neurological</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Seizures or Neurological', 'value': 'seizures'}</t>
+          <t>Seizures or Neurological</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'frequent_ear_infections',_'value':_'ear'}</t>
+          <t>frequent_ear_infections</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Frequent Ear Infections', 'value': 'ear'}</t>
+          <t>Frequent Ear Infections</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_minimal_to_no_pain',_'value':_'1'}</t>
+          <t>1_-_minimal_to_no_pain</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': '1 - Minimal to No Pain', 'value': '1'}</t>
+          <t>1 - Minimal to No Pain</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'5_-_moderate_pain',_'value':_'5'}</t>
+          <t>5_-_moderate_pain</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': '5 - Moderate Pain', 'value': '5'}</t>
+          <t>5 - Moderate Pain</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'10_-_severe_pain',_'value':_'10'}</t>
+          <t>10_-_severe_pain</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': '10 - Severe Pain', 'value': '10'}</t>
+          <t>10 - Severe Pain</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'high_appetite',_'value':_'high'}</t>
+          <t>high_appetite</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'High Appetite', 'value': 'high'}</t>
+          <t>High Appetite</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'normal_appetite',_'value':_'normal'}</t>
+          <t>normal_appetite</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Normal Appetite', 'value': 'normal'}</t>
+          <t>Normal Appetite</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'low_appetite',_'value':_'low'}</t>
+          <t>low_appetite</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Low Appetite', 'value': 'low'}</t>
+          <t>Low Appetite</t>
         </is>
       </c>
     </row>
